--- a/hall/resources/sample/VisitorGenWatchVideo.xlsx
+++ b/hall/resources/sample/VisitorGenWatchVideo.xlsx
@@ -50,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>序号ID</t>
   </si>
@@ -95,9 +95,6 @@
     <t>单个游客数量</t>
   </si>
   <si>
-    <t>单日观看次数上限</t>
-  </si>
-  <si>
     <t>观看CD时间（min）</t>
   </si>
   <si>
@@ -119,15 +116,54 @@
     <t>VisitorCount</t>
   </si>
   <si>
-    <t>DailyViewLimit</t>
-  </si>
-  <si>
     <t>ViewCD</t>
   </si>
   <si>
     <t>icon</t>
   </si>
   <si>
+    <t>街头潮人</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>复古绅士</t>
+  </si>
+  <si>
+    <t>酷盖少年</t>
+  </si>
+  <si>
+    <t>潮流先锋</t>
+  </si>
+  <si>
+    <t>时尚教主</t>
+  </si>
+  <si>
+    <t>街拍达人</t>
+  </si>
+  <si>
+    <t>运动健将</t>
+  </si>
+  <si>
+    <t>绿</t>
+  </si>
+  <si>
+    <t>跑酷少年</t>
+  </si>
+  <si>
+    <t>滑板高手</t>
+  </si>
+  <si>
+    <t>甜心辣妹</t>
+  </si>
+  <si>
+    <t>活力少女</t>
+  </si>
+  <si>
+    <t>优雅女神</t>
+  </si>
+  <si>
     <t>健身狂魔</t>
   </si>
   <si>
@@ -140,13 +176,13 @@
     <t>登山行者</t>
   </si>
   <si>
-    <t>马拉松客</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>极限玩家</t>
+    <t>文艺青年</t>
+  </si>
+  <si>
+    <t>书香少女</t>
+  </si>
+  <si>
+    <t>民谣歌手</t>
   </si>
 </sst>
 </file>
@@ -812,7 +848,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1347,16 +1383,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
-    <col min="7" max="7" width="17.625" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="6" max="6" width="17.625" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1372,176 +1407,409 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
+    </row>
+    <row r="5" ht="16.5" spans="1:7">
       <c r="A5">
         <v>1001</v>
       </c>
       <c r="B5" s="4">
-        <v>1025301</v>
+        <v>1025101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5">
         <v>30</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:8">
+    <row r="6" ht="16.5" spans="1:7">
       <c r="A6">
         <v>1002</v>
       </c>
       <c r="B6" s="4">
-        <v>1025302</v>
+        <v>1025102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
         <v>30</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:8">
+    <row r="7" ht="16.5" spans="1:7">
       <c r="A7">
         <v>1003</v>
       </c>
       <c r="B7" s="4">
-        <v>1025303</v>
+        <v>1025103</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7">
         <v>30</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:8">
+    <row r="8" ht="16.5" spans="1:7">
       <c r="A8">
         <v>1004</v>
       </c>
       <c r="B8" s="4">
-        <v>1025401</v>
+        <v>1025104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8">
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:8">
+    <row r="9" ht="16.5" spans="1:7">
       <c r="A9">
         <v>1005</v>
       </c>
       <c r="B9" s="4">
-        <v>1025402</v>
+        <v>1025105</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:7">
+      <c r="A10">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1025106</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:7">
+      <c r="A11">
+        <v>1007</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1025201</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9">
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
         <v>30</v>
       </c>
     </row>
+    <row r="12" ht="16.5" spans="1:7">
+      <c r="A12">
+        <v>1008</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1025202</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:7">
+      <c r="A13">
+        <v>1009</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1025203</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>5</v>
+      </c>
+      <c r="F13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:7">
+      <c r="A14">
+        <v>1010</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1025204</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14">
+        <v>5</v>
+      </c>
+      <c r="F14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:7">
+      <c r="A15">
+        <v>1011</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1025205</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:7">
+      <c r="A16">
+        <v>1012</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1025206</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:6">
+      <c r="A17">
+        <v>1013</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1025301</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:6">
+      <c r="A18">
+        <v>1014</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1025302</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:6">
+      <c r="A19">
+        <v>1015</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1025303</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19">
+        <v>5</v>
+      </c>
+      <c r="F19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:6">
+      <c r="A20">
+        <v>1016</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1025304</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:6">
+      <c r="A21">
+        <v>1017</v>
+      </c>
+      <c r="B21" s="4">
+        <v>1025305</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:6">
+      <c r="A22">
+        <v>1018</v>
+      </c>
+      <c r="B22" s="4">
+        <v>1025306</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B7">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:B9">
+  <conditionalFormatting sqref="B5:B22">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
